--- a/app/config/tables/refrigerators/forms/refrigerators/refrigerators.xlsx
+++ b/app/config/tables/refrigerators/forms/refrigerators/refrigerators.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clarice\cold-chain\cold-chain-app-designer\app\config\tables\refrigerators\forms\refrigerators\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Projects\ODK-X\our-work\app\config\tables\refrigerators\forms\refrigerators\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD95175-EC72-4B98-B93E-9162B1889CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="0" windowWidth="26940" windowHeight="13536" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="8" r:id="rId1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="421">
   <si>
     <t>comments</t>
   </si>
@@ -1292,11 +1293,17 @@
   <si>
     <t>(false)</t>
   </si>
+  <si>
+    <t>is_under_pmm</t>
+  </si>
+  <si>
+    <t>Is Under PMM Surveillance?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
@@ -1415,19 +1422,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1439,65 +1444,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1510,10 +1473,10 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="6"/>
-    <cellStyle name="Normal 2 2" xfId="7"/>
-    <cellStyle name="Normal 2 3" xfId="9"/>
-    <cellStyle name="Normal 3" xfId="8"/>
+    <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 2 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -1917,45 +1880,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" style="50"/>
-    <col min="3" max="3" width="19.5546875" style="50" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" style="50" customWidth="1"/>
-    <col min="5" max="16384" width="9.5546875" style="50"/>
+    <col min="1" max="1" width="17.453125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" style="20"/>
+    <col min="3" max="3" width="19.54296875" style="20" customWidth="1"/>
+    <col min="4" max="4" width="26.453125" style="20" customWidth="1"/>
+    <col min="5" max="16384" width="9.54296875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-    </row>
-    <row r="3" spans="1:4" ht="78" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+    </row>
+    <row r="3" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19" t="s">
         <v>387</v>
       </c>
     </row>
@@ -1966,23 +1929,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V65"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:V66"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.77734375" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="42.44140625" customWidth="1"/>
-    <col min="6" max="6" width="24.5546875" customWidth="1"/>
-    <col min="7" max="7" width="29.5546875" customWidth="1"/>
-    <col min="8" max="9" width="30.44140625" customWidth="1"/>
-    <col min="10" max="10" width="41.5546875" customWidth="1"/>
-    <col min="11" max="12" width="22.77734375" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="14" max="15" width="20.21875" customWidth="1"/>
-    <col min="16" max="16" width="16.21875" customWidth="1"/>
-    <col min="17" max="1029" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="42.81640625" customWidth="1"/>
+    <col min="2" max="3" width="11.453125" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="42.453125" customWidth="1"/>
+    <col min="6" max="6" width="24.54296875" customWidth="1"/>
+    <col min="7" max="7" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="30.453125" customWidth="1"/>
+    <col min="10" max="10" width="41.54296875" customWidth="1"/>
+    <col min="11" max="12" width="22.81640625" customWidth="1"/>
+    <col min="13" max="13" width="19.54296875" customWidth="1"/>
+    <col min="14" max="15" width="20.1796875" customWidth="1"/>
+    <col min="16" max="16" width="16.1796875" customWidth="1"/>
+    <col min="17" max="1029" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -2010,16 +1973,16 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="2" t="s">
         <v>276</v>
       </c>
       <c r="M1" t="s">
@@ -2028,7 +1991,7 @@
       <c r="N1" t="s">
         <v>184</v>
       </c>
-      <c r="O1" s="41" t="s">
+      <c r="O1" t="s">
         <v>415</v>
       </c>
       <c r="P1" t="s">
@@ -2037,33 +2000,30 @@
       <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" t="s">
         <v>181</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="I2" s="17"/>
-      <c r="L2" s="23"/>
-    </row>
-    <row r="3" spans="1:22" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
       <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
@@ -2073,28 +2033,22 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="27"/>
+      <c r="I3" s="2"/>
+      <c r="L3" s="2"/>
       <c r="R3" t="s">
         <v>257</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-    </row>
-    <row r="4" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="L4" s="23"/>
-    </row>
-    <row r="5" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>18</v>
       </c>
@@ -2110,7 +2064,7 @@
       <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" t="s">
         <v>259</v>
       </c>
       <c r="J5" t="s">
@@ -2119,7 +2073,7 @@
       <c r="K5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="L5" s="13" t="s">
         <v>259</v>
       </c>
       <c r="S5">
@@ -2127,105 +2081,95 @@
       </c>
     </row>
     <row r="6" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="I6" s="17"/>
-      <c r="L6" s="23"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:22" s="41" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="41" t="s">
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" t="s">
         <v>398</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:22" s="41" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="3" t="s">
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" t="s">
         <v>260</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K8" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="42" t="s">
+      <c r="L8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="41" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="41" t="s">
+    <row r="9" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="I9" s="42"/>
-      <c r="L9" s="42"/>
-    </row>
-    <row r="10" spans="1:22" s="43" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="D10" s="44" t="s">
+    </row>
+    <row r="10" spans="1:22" s="16" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="D10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="H10" s="43" t="s">
+      <c r="H10" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="J10" s="43" t="s">
+      <c r="J10" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="K10" s="43" t="s">
+      <c r="K10" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="P10" s="52"/>
-    </row>
-    <row r="11" spans="1:22" s="41" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="41" t="s">
+      <c r="P10" s="22"/>
+    </row>
+    <row r="11" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" t="s">
         <v>380</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="P11" s="6"/>
+      <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="3" t="s">
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="3"/>
       <c r="F12" t="s">
         <v>248</v>
       </c>
@@ -2235,11 +2179,9 @@
       <c r="H12" t="s">
         <v>250</v>
       </c>
-      <c r="I12" s="18"/>
       <c r="J12" t="s">
         <v>251</v>
       </c>
-      <c r="L12" s="23"/>
       <c r="M12" t="s">
         <v>253</v>
       </c>
@@ -2247,33 +2189,28 @@
         <v>254</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="43" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="44" t="s">
+    <row r="13" spans="1:22" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="E13" s="44"/>
-      <c r="J13" s="43" t="s">
+      <c r="J13" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="K13" s="43" t="s">
+      <c r="K13" s="16" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="41" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="41" t="s">
+    <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="I14" s="42"/>
-    </row>
-    <row r="15" spans="1:22" s="41" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="41" t="s">
+    </row>
+    <row r="15" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="P15" s="6"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
@@ -2282,81 +2219,65 @@
       <c r="C16" t="s">
         <v>380</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="I16" s="17"/>
-      <c r="L16" s="23"/>
-    </row>
-    <row r="17" spans="1:22" s="41" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="41" t="s">
+    </row>
+    <row r="17" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="1:22" s="41" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="3" t="s">
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="41" t="s">
+      <c r="H18" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="42" t="s">
+      <c r="I18" t="s">
         <v>260</v>
       </c>
-      <c r="J18" s="41" t="s">
+      <c r="J18" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="41" t="s">
+      <c r="K18" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="42" t="s">
+      <c r="L18" t="s">
         <v>277</v>
       </c>
-      <c r="S18" s="41" t="s">
+      <c r="S18" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="I19" s="17"/>
-      <c r="L19" s="23"/>
-    </row>
-    <row r="20" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="I20" s="17"/>
-      <c r="L20" s="23"/>
-    </row>
-    <row r="21" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="3" t="s">
+    </row>
+    <row r="22" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="3"/>
       <c r="F22" t="s">
         <v>34</v>
       </c>
@@ -2366,7 +2287,7 @@
       <c r="H22" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" t="s">
         <v>261</v>
       </c>
       <c r="J22" t="s">
@@ -2375,15 +2296,14 @@
       <c r="K22" t="s">
         <v>36</v>
       </c>
-      <c r="L22" s="24" t="s">
+      <c r="L22" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="3" t="s">
+    <row r="23" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
         <v>179</v>
       </c>
-      <c r="E23" s="3"/>
       <c r="F23" t="s">
         <v>357</v>
       </c>
@@ -2393,7 +2313,7 @@
       <c r="H23" t="s">
         <v>39</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" t="s">
         <v>263</v>
       </c>
       <c r="J23" t="s">
@@ -2402,7 +2322,7 @@
       <c r="K23" t="s">
         <v>39</v>
       </c>
-      <c r="L23" s="24" t="s">
+      <c r="L23" t="s">
         <v>280</v>
       </c>
       <c r="M23" t="s">
@@ -2421,111 +2341,103 @@
         <v>413</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="43" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="44" t="s">
+    <row r="24" spans="1:22" s="16" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="G24" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="H24" s="43" t="s">
+      <c r="H24" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="I24" s="43" t="s">
+      <c r="I24" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="J24" s="43" t="s">
+      <c r="J24" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="K24" s="43" t="s">
+      <c r="K24" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="L24" s="43" t="s">
+      <c r="L24" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="M24" s="43" t="s">
+      <c r="M24" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="N24" s="43" t="s">
+      <c r="N24" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="T24" s="43" t="s">
+      <c r="T24" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="U24" s="43" t="s">
+      <c r="U24" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="V24" s="43" t="s">
+      <c r="V24" s="16" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:22" s="41" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
+    </row>
+    <row r="26" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>216</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" t="s">
         <v>418</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:22" s="43" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="45" t="s">
+    </row>
+    <row r="27" spans="1:22" s="16" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="K27" s="45" t="s">
+      <c r="K27" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="L27" s="45"/>
-      <c r="M27" s="43" t="s">
+      <c r="L27" s="17"/>
+      <c r="M27" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="N27" s="43" t="s">
+      <c r="N27" s="16" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="42" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
+    <row r="28" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-    </row>
-    <row r="29" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="3" t="s">
+      <c r="D28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+    </row>
+    <row r="29" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="3"/>
       <c r="F29" t="s">
         <v>185</v>
       </c>
@@ -2535,7 +2447,7 @@
       <c r="H29" t="s">
         <v>187</v>
       </c>
-      <c r="I29" s="18" t="s">
+      <c r="I29" t="s">
         <v>262</v>
       </c>
       <c r="J29" t="s">
@@ -2544,24 +2456,20 @@
       <c r="K29" t="s">
         <v>189</v>
       </c>
-      <c r="L29" s="24" t="s">
+      <c r="L29" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="I30" s="17"/>
-      <c r="L30" s="23"/>
-    </row>
-    <row r="31" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="3" t="s">
+    </row>
+    <row r="31" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="13" t="s">
         <v>224</v>
       </c>
       <c r="F31" t="s">
@@ -2573,7 +2481,7 @@
       <c r="H31" t="s">
         <v>193</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I31" t="s">
         <v>264</v>
       </c>
       <c r="J31" t="s">
@@ -2582,28 +2490,23 @@
       <c r="K31" t="s">
         <v>194</v>
       </c>
-      <c r="L31" s="24" t="s">
+      <c r="L31" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
         <v>195</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="I32" s="17"/>
-      <c r="L32" s="23"/>
-    </row>
-    <row r="33" spans="2:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3" t="s">
+      <c r="F33" t="s">
         <v>196</v>
       </c>
       <c r="G33" t="s">
@@ -2612,7 +2515,7 @@
       <c r="H33" t="s">
         <v>199</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="3" t="s">
         <v>265</v>
       </c>
       <c r="J33" t="s">
@@ -2621,65 +2524,52 @@
       <c r="K33" t="s">
         <v>201</v>
       </c>
-      <c r="L33" s="25" t="s">
+      <c r="L33" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="43" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="44" t="s">
+    <row r="34" spans="2:12" s="16" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D34" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="43" t="s">
+      <c r="G34" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="H34" s="43" t="s">
+      <c r="H34" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="I34" s="53" t="s">
+      <c r="I34" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="J34" s="43" t="s">
+      <c r="J34" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="K34" s="43" t="s">
+      <c r="K34" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="L34" s="53" t="s">
+      <c r="L34" s="23" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="35" spans="2:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="I35" s="17"/>
-      <c r="L35" s="23"/>
-    </row>
-    <row r="36" spans="2:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="I36" s="17"/>
-      <c r="L36" s="23"/>
-    </row>
-    <row r="37" spans="2:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="I37" s="17"/>
-      <c r="L37" s="23"/>
-    </row>
-    <row r="38" spans="2:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>24</v>
       </c>
@@ -2695,7 +2585,7 @@
       <c r="H38" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="18" t="s">
+      <c r="I38" t="s">
         <v>267</v>
       </c>
       <c r="J38" t="s">
@@ -2704,7 +2594,7 @@
       <c r="K38" t="s">
         <v>44</v>
       </c>
-      <c r="L38" s="24" t="s">
+      <c r="L38" t="s">
         <v>284</v>
       </c>
     </row>
@@ -2724,7 +2614,7 @@
       <c r="H39" t="s">
         <v>49</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I39" t="s">
         <v>268</v>
       </c>
       <c r="J39" t="s">
@@ -2733,11 +2623,11 @@
       <c r="K39" t="s">
         <v>51</v>
       </c>
-      <c r="L39" s="26" t="s">
+      <c r="L39" s="13" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="2:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
         <v>24</v>
       </c>
@@ -2753,7 +2643,7 @@
       <c r="H40" t="s">
         <v>53</v>
       </c>
-      <c r="I40" s="18" t="s">
+      <c r="I40" t="s">
         <v>269</v>
       </c>
       <c r="J40" t="s">
@@ -2762,12 +2652,12 @@
       <c r="K40" t="s">
         <v>54</v>
       </c>
-      <c r="L40" s="24" t="s">
+      <c r="L40" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>217</v>
       </c>
       <c r="E41" t="s">
@@ -2782,7 +2672,7 @@
       <c r="H41" t="s">
         <v>58</v>
       </c>
-      <c r="I41" s="18" t="s">
+      <c r="I41" t="s">
         <v>270</v>
       </c>
       <c r="J41" t="s">
@@ -2791,7 +2681,7 @@
       <c r="K41" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="24" t="s">
+      <c r="L41" t="s">
         <v>287</v>
       </c>
     </row>
@@ -2811,7 +2701,7 @@
       <c r="H42" t="s">
         <v>166</v>
       </c>
-      <c r="I42" s="18" t="s">
+      <c r="I42" t="s">
         <v>271</v>
       </c>
       <c r="J42" t="s">
@@ -2820,7 +2710,7 @@
       <c r="K42" t="s">
         <v>168</v>
       </c>
-      <c r="L42" s="28" t="s">
+      <c r="L42" s="3" t="s">
         <v>288</v>
       </c>
     </row>
@@ -2828,14 +2718,12 @@
       <c r="B43" t="s">
         <v>30</v>
       </c>
-      <c r="I43" s="17"/>
-      <c r="L43" s="23"/>
-    </row>
-    <row r="44" spans="2:12" s="41" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="41" t="s">
+    </row>
+    <row r="44" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" t="s">
         <v>331</v>
       </c>
     </row>
@@ -2843,17 +2731,15 @@
       <c r="B45" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="17"/>
-      <c r="L45" s="23"/>
     </row>
     <row r="46" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" t="s">
         <v>61</v>
       </c>
       <c r="G46" t="s">
@@ -2862,7 +2748,7 @@
       <c r="H46" t="s">
         <v>63</v>
       </c>
-      <c r="I46" s="19" t="s">
+      <c r="I46" t="s">
         <v>272</v>
       </c>
       <c r="J46" t="s">
@@ -2871,7 +2757,7 @@
       <c r="K46" t="s">
         <v>65</v>
       </c>
-      <c r="L46" s="26" t="s">
+      <c r="L46" s="13" t="s">
         <v>289</v>
       </c>
     </row>
@@ -2882,30 +2768,28 @@
       <c r="C47" t="s">
         <v>205</v>
       </c>
-      <c r="I47" s="17"/>
-      <c r="L47" s="23"/>
-    </row>
-    <row r="48" spans="2:12" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="43" t="s">
+    </row>
+    <row r="48" spans="2:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F48" s="43" t="s">
+      <c r="F48" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="G48" s="43" t="s">
+      <c r="G48" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="H48" s="43" t="s">
+      <c r="H48" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="J48" s="43" t="s">
+      <c r="J48" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="K48" s="43" t="s">
+      <c r="K48" s="16" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="49" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" ht="25" x14ac:dyDescent="0.25">
       <c r="D49" t="s">
         <v>24</v>
       </c>
@@ -2921,7 +2805,7 @@
       <c r="H49" t="s">
         <v>208</v>
       </c>
-      <c r="I49" s="22" t="s">
+      <c r="I49" s="3" t="s">
         <v>273</v>
       </c>
       <c r="J49" t="s">
@@ -2930,7 +2814,7 @@
       <c r="K49" t="s">
         <v>210</v>
       </c>
-      <c r="L49" s="29" t="s">
+      <c r="L49" s="14" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2938,18 +2822,14 @@
       <c r="B50" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="17"/>
-      <c r="L50" s="23"/>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>30</v>
       </c>
-      <c r="I51" s="17"/>
-      <c r="L51" s="23"/>
-    </row>
-    <row r="52" spans="2:12" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="41" t="s">
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2957,10 +2837,8 @@
       <c r="B53" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="17"/>
-      <c r="L53" s="23"/>
-    </row>
-    <row r="54" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="2:12" ht="25" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
         <v>24</v>
       </c>
@@ -2976,7 +2854,7 @@
       <c r="H54" t="s">
         <v>213</v>
       </c>
-      <c r="I54" s="22" t="s">
+      <c r="I54" s="3" t="s">
         <v>274</v>
       </c>
       <c r="J54" t="s">
@@ -2985,7 +2863,7 @@
       <c r="K54" t="s">
         <v>215</v>
       </c>
-      <c r="L54" s="26" t="s">
+      <c r="L54" s="13" t="s">
         <v>291</v>
       </c>
     </row>
@@ -2996,10 +2874,8 @@
       <c r="C55" t="s">
         <v>363</v>
       </c>
-      <c r="I55" s="17"/>
-      <c r="L55" s="23"/>
-    </row>
-    <row r="56" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="2:12" ht="25" x14ac:dyDescent="0.25">
       <c r="D56" t="s">
         <v>33</v>
       </c>
@@ -3012,7 +2888,7 @@
       <c r="H56" t="s">
         <v>221</v>
       </c>
-      <c r="I56" s="22" t="s">
+      <c r="I56" s="3" t="s">
         <v>275</v>
       </c>
       <c r="J56" t="s">
@@ -3021,116 +2897,131 @@
       <c r="K56" t="s">
         <v>223</v>
       </c>
-      <c r="L56" s="26" t="s">
+      <c r="L56" s="13" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="57" spans="2:12" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="41" t="s">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="41" t="s">
+      <c r="E57" t="s">
         <v>52</v>
       </c>
-      <c r="F57" s="41" t="s">
+      <c r="F57" t="s">
         <v>364</v>
       </c>
-      <c r="G57" s="41" t="s">
+      <c r="G57" t="s">
         <v>365</v>
       </c>
-      <c r="H57" s="41" t="s">
+      <c r="H57" t="s">
         <v>366</v>
       </c>
-      <c r="I57" s="28"/>
-      <c r="J57" s="41" t="s">
+      <c r="I57" s="3"/>
+      <c r="J57" t="s">
         <v>367</v>
       </c>
-      <c r="K57" s="41" t="s">
+      <c r="K57" t="s">
         <v>368</v>
       </c>
-      <c r="L57" s="34"/>
+      <c r="L57" s="13"/>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>23</v>
       </c>
-      <c r="I58" s="17"/>
-      <c r="L58" s="23"/>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>30</v>
       </c>
-      <c r="I59" s="17"/>
-      <c r="L59" s="23"/>
-    </row>
-    <row r="60" spans="2:12" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="41" t="s">
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="41" t="s">
+      <c r="C60" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="2:12" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="41" t="s">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="2:12" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D62" s="43" t="s">
+    <row r="62" spans="2:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D62" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="43" t="s">
+      <c r="E62" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="43" t="s">
+      <c r="F62" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="G62" s="43" t="s">
+      <c r="G62" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="H62" s="43" t="s">
+      <c r="H62" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="J62" s="43" t="s">
+      <c r="J62" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="K62" s="43" t="s">
+      <c r="K62" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="L62" s="45"/>
-    </row>
-    <row r="63" spans="2:12" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="42" t="s">
+      <c r="L62" s="17"/>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>30</v>
       </c>
-      <c r="L63" s="34"/>
+      <c r="L63" s="13"/>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="4:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D65" s="43" t="s">
+    <row r="65" spans="4:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F65" s="43" t="s">
+      <c r="F65" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="G65" s="43" t="s">
+      <c r="G65" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="H65" s="43" t="s">
+      <c r="H65" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="J65" s="43" t="s">
+      <c r="J65" s="16" t="s">
         <v>406</v>
       </c>
-      <c r="K65" s="43" t="s">
+      <c r="K65" s="16" t="s">
         <v>408</v>
       </c>
+    </row>
+    <row r="66" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" t="s">
+        <v>60</v>
+      </c>
+      <c r="F66" t="s">
+        <v>419</v>
+      </c>
+      <c r="G66" t="s">
+        <v>420</v>
+      </c>
+      <c r="I66" s="3"/>
+      <c r="J66" t="s">
+        <v>420</v>
+      </c>
+      <c r="L66" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -3139,191 +3030,190 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" customWidth="1"/>
-    <col min="2" max="2" width="33.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="1025" width="8.5546875" customWidth="1"/>
+    <col min="6" max="1025" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:5" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="4" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:5" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:5" s="3" customFormat="1" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:5" s="3" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="4" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="4" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="E7" s="38"/>
-    </row>
-    <row r="8" spans="1:5" s="41" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+    <row r="7" spans="1:5" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" t="s">
         <v>369</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>370</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="41" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="12" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="43" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+    <row r="11" spans="1:5" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="E11" s="44"/>
-    </row>
-    <row r="12" spans="1:5" s="43" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+    </row>
+    <row r="12" spans="1:5" s="16" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="E12" s="46"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="18"/>
+    </row>
+    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -3336,41 +3226,41 @@
       <c r="D14" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="13" t="s">
         <v>233</v>
       </c>
       <c r="D15" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="13" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="43" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+    <row r="16" spans="1:5" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="17" t="s">
         <v>300</v>
       </c>
     </row>
@@ -3378,156 +3268,156 @@
       <c r="A17" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="13" t="s">
         <v>236</v>
       </c>
       <c r="D17" t="s">
         <v>237</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="13" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="13" t="s">
         <v>239</v>
       </c>
       <c r="D18" t="s">
         <v>240</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="13" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="13" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="13" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="13" t="s">
         <v>87</v>
       </c>
       <c r="D20" t="s">
         <v>244</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="13" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="E21" s="34"/>
-    </row>
-    <row r="23" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
+    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="E21" s="13"/>
+    </row>
+    <row r="23" spans="1:5" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="E23" s="46"/>
-    </row>
-    <row r="24" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="E24" s="46"/>
-    </row>
-    <row r="25" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43" t="s">
+      <c r="E24" s="18"/>
+    </row>
+    <row r="25" spans="1:5" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E25" s="46"/>
-    </row>
-    <row r="26" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="43" t="s">
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="E26" s="46"/>
-    </row>
-    <row r="27" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43" t="s">
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="D27" s="43" t="s">
+      <c r="D27" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="E27" s="46"/>
-    </row>
-    <row r="28" spans="1:5" s="41" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="34"/>
-    </row>
-    <row r="30" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="13"/>
+    </row>
+    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>224</v>
       </c>
       <c r="B30" t="s">
@@ -3539,12 +3429,12 @@
       <c r="D30" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="13" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:5" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>224</v>
       </c>
       <c r="B31" t="s">
@@ -3556,12 +3446,12 @@
       <c r="D31" t="s">
         <v>93</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="13" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+    <row r="32" spans="1:5" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>224</v>
       </c>
       <c r="B32" t="s">
@@ -3573,11 +3463,11 @@
       <c r="D32" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="34" t="s">
+      <c r="E32" s="13" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3590,11 +3480,11 @@
       <c r="D35" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3607,7 +3497,7 @@
       <c r="D36" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E36" s="15" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3624,7 +3514,7 @@
       <c r="D37" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="35" t="s">
+      <c r="E37" s="15" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3641,7 +3531,7 @@
       <c r="D38" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="35" t="s">
+      <c r="E38" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3658,7 +3548,7 @@
       <c r="D39" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="35" t="s">
+      <c r="E39" s="15" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3675,7 +3565,6 @@
       <c r="D40" t="s">
         <v>106</v>
       </c>
-      <c r="E40" s="30"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -3690,7 +3579,7 @@
       <c r="D43" t="s">
         <v>178</v>
       </c>
-      <c r="E43" s="31" t="s">
+      <c r="E43" t="s">
         <v>304</v>
       </c>
     </row>
@@ -3707,7 +3596,7 @@
       <c r="D44" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="31" t="s">
+      <c r="E44" t="s">
         <v>308</v>
       </c>
     </row>
@@ -3724,7 +3613,7 @@
       <c r="D45" t="s">
         <v>176</v>
       </c>
-      <c r="E45" s="31" t="s">
+      <c r="E45" t="s">
         <v>309</v>
       </c>
     </row>
@@ -3741,109 +3630,109 @@
       <c r="D46" t="s">
         <v>177</v>
       </c>
-      <c r="E46" s="31" t="s">
+      <c r="E46" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" s="34" t="s">
+      <c r="E48" s="13" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="13" t="s">
         <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="34" t="s">
+      <c r="E49" s="13" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" s="34" t="s">
+      <c r="E51" s="13" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="13" t="s">
         <v>93</v>
       </c>
       <c r="D52" t="s">
         <v>93</v>
       </c>
-      <c r="E52" s="34" t="s">
+      <c r="E52" s="13" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E53" s="34" t="s">
+      <c r="E53" s="13" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="13" t="s">
         <v>229</v>
       </c>
       <c r="D56" t="s">
         <v>230</v>
       </c>
-      <c r="E56" s="34" t="s">
+      <c r="E56" s="13" t="s">
         <v>312</v>
       </c>
     </row>
@@ -3854,48 +3743,48 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" customWidth="1"/>
-    <col min="7" max="9" width="39.5546875" customWidth="1"/>
-    <col min="10" max="10" width="39.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="7" max="9" width="39.54296875" customWidth="1"/>
+    <col min="10" max="10" width="39.453125" customWidth="1"/>
     <col min="11" max="11" width="43" customWidth="1"/>
-    <col min="12" max="1025" width="10.77734375" customWidth="1"/>
+    <col min="12" max="1025" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>115</v>
       </c>
       <c r="J1" t="s">
@@ -3905,8 +3794,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -3918,15 +3807,15 @@
       <c r="D2" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="4"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="3"/>
       <c r="J2" t="s">
         <v>120</v>
       </c>
@@ -3934,7 +3823,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -3950,12 +3839,12 @@
       <c r="E3" t="s">
         <v>245</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="4"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="3"/>
       <c r="J3" t="s">
         <v>120</v>
       </c>
@@ -3975,155 +3864,155 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AMK9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="10.77734375" style="11" customWidth="1"/>
-    <col min="3" max="3" width="34.44140625" style="11" customWidth="1"/>
-    <col min="4" max="1025" width="10.77734375" style="11" customWidth="1"/>
+    <col min="1" max="2" width="10.81640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" style="9" customWidth="1"/>
+    <col min="4" max="1025" width="10.81640625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="12"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4139,22 +4028,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" style="30" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
-    <col min="8" max="1026" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" customWidth="1"/>
+    <col min="8" max="1026" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" ht="16.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>144</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -4166,7 +4055,7 @@
       <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" t="s">
         <v>258</v>
       </c>
       <c r="F1" t="s">
@@ -4175,54 +4064,47 @@
       <c r="G1" t="s">
         <v>146</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="H2" s="41"/>
-    </row>
-    <row r="3" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="16.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="H3" s="41"/>
-    </row>
-    <row r="4" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" ht="16.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B4" s="2">
         <v>20170804</v>
       </c>
-      <c r="E4" s="36"/>
-      <c r="H4" s="41"/>
-    </row>
-    <row r="5" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="16.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>152</v>
       </c>
       <c r="D5" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" t="s">
         <v>313</v>
       </c>
-      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -4231,21 +4113,18 @@
       <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="36"/>
       <c r="F7" t="s">
         <v>156</v>
       </c>
       <c r="G7" t="s">
         <v>157</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4253,32 +4132,27 @@
       <c r="A8" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="36"/>
       <c r="F8" t="s">
         <v>159</v>
       </c>
       <c r="G8" t="s">
         <v>160</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="40" t="s">
+      <c r="F9" t="s">
         <v>315</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" t="s">
         <v>319</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4289,11 +4163,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4327,13 +4201,13 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" t="s">
         <v>377</v>
       </c>
-      <c r="C4" s="41" t="b">
+      <c r="C4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4353,35 +4227,35 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" customWidth="1"/>
-    <col min="2" max="2" width="42.77734375" customWidth="1"/>
+    <col min="1" max="1" width="34.453125" customWidth="1"/>
+    <col min="2" max="2" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>359</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="3" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="41" customFormat="1" ht="145.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+    <row r="3" spans="1:2" ht="137.5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>360</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="3" t="s">
         <v>414</v>
       </c>
     </row>
